--- a/assets/data/excel/enemies.xlsx
+++ b/assets/data/excel/enemies.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -499,25 +499,20 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>baseDef</t>
+          <t>baseSpd</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>baseSpd</t>
+          <t>skills</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>skills</t>
+          <t>description</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>dropTable</t>
         </is>
@@ -566,20 +561,15 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>array</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>array</t>
+          <t>string</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>array</t>
         </is>
@@ -623,25 +613,20 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>基础防御</t>
+          <t>基础速度</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>基础速度</t>
+          <t>技能列表</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>技能列表</t>
+          <t>描述</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>描述</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>掉落表</t>
         </is>
@@ -680,22 +665,19 @@
         <v>45</v>
       </c>
       <c r="H4" t="n">
-        <v>30</v>
-      </c>
-      <c r="I4" t="n">
         <v>28</v>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>废弃矿区内常见的变异蜥蜴，体表覆盖铁锈色鳞甲，尾部可喷射高温蒸汽。行动迟缓但咬合力惊人，被咬中的猎物伤口会因高温而难以愈合。</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
-        <is>
-          <t>废弃矿区内常见的变异蜥蜴，体表覆盖铁锈色鳞甲，尾部可喷射高温蒸汽。行动迟缓但咬合力惊人，被咬中的猎物伤口会因高温而难以愈合。</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
         <is>
           <t>[{"type": "mycelium", "min": 5, "max": 15}]</t>
         </is>
@@ -734,22 +716,19 @@
         <v>35</v>
       </c>
       <c r="H5" t="n">
-        <v>15</v>
-      </c>
-      <c r="I5" t="n">
         <v>42</v>
       </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>吸收了辐射粉尘后体型膨胀至掌心大小的飞蛾，翅膀振动时会散播有毒孢子。群聚时形成的孢子云可覆盖整个矿区通道。</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
-        <is>
-          <t>吸收了辐射粉尘后体型膨胀至掌心大小的飞蛾，翅膀振动时会散播有毒孢子。群聚时形成的孢子云可覆盖整个矿区通道。</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
         <is>
           <t>[{"type": "mycelium", "min": 3, "max": 10}]</t>
         </is>
@@ -788,22 +767,19 @@
         <v>40</v>
       </c>
       <c r="H6" t="n">
-        <v>20</v>
-      </c>
-      <c r="I6" t="n">
         <v>18</v>
       </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>沉没水城中漂浮的变异水母，触须分泌的酸性液体可在30秒内腐蚀标准防护服。通常成群结队出没于废弃蓄水池中。</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
-        <is>
-          <t>沉没水城中漂浮的变异水母，触须分泌的酸性液体可在30秒内腐蚀标准防护服。通常成群结队出没于废弃蓄水池中。</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
         <is>
           <t>[{"type": "mycelium", "min": 8, "max": 18}]</t>
         </is>
@@ -842,22 +818,19 @@
         <v>30</v>
       </c>
       <c r="H7" t="n">
-        <v>50</v>
-      </c>
-      <c r="I7" t="n">
         <v>10</v>
       </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>融合了废弃电缆基因的变异藤蔓，以金属离子为养分生长。根系可延伸至地下50米，感应到震动后会缠绞经过的生物。</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
-        <is>
-          <t>融合了废弃电缆基因的变异藤蔓，以金属离子为养分生长。根系可延伸至地下50米，感应到震动后会缠绞经过的生物。</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
         <is>
           <t>[{"type": "mycelium", "min": 6, "max": 14}]</t>
         </is>
@@ -896,22 +869,19 @@
         <v>25</v>
       </c>
       <c r="H8" t="n">
-        <v>12</v>
-      </c>
-      <c r="I8" t="n">
         <v>50</v>
       </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>体表附着生物荧光苔藓的变异鼠类，在黑暗中发出幽蓝光芒。虽个体弱小但繁殖力极强，常以百为单位成群出没。</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
-        <is>
-          <t>体表附着生物荧光苔藓的变异鼠类，在黑暗中发出幽蓝光芒。虽个体弱小但繁殖力极强，常以百为单位成群出没。</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
         <is>
           <t>[{"type": "mycelium", "min": 2, "max": 8}]</t>
         </is>
@@ -950,22 +920,19 @@
         <v>50</v>
       </c>
       <c r="H9" t="n">
-        <v>35</v>
-      </c>
-      <c r="I9" t="n">
         <v>15</v>
       </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>栖息于污染水域的巨型蟾蜍，皮肤持续分泌pH值低于1的强酸。跳跃攻击可将酸液溅射至5米范围内，腐蚀一切有机与无机物质。</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
-        <is>
-          <t>栖息于污染水域的巨型蟾蜍，皮肤持续分泌pH值低于1的强酸。跳跃攻击可将酸液溅射至5米范围内，腐蚀一切有机与无机物质。</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
         <is>
           <t>[{"type": "mycelium", "min": 8, "max": 20}]</t>
         </is>
@@ -1004,22 +971,19 @@
         <v>55</v>
       </c>
       <c r="H10" t="n">
-        <v>60</v>
-      </c>
-      <c r="I10" t="n">
         <v>12</v>
       </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>以废弃金属为甲壳的变异螃蟹，钳臂可夹断直径10厘米的钢管。移动缓慢但防御极高，常堵塞通道形成天然路障。</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
-        <is>
-          <t>以废弃金属为甲壳的变异螃蟹，钳臂可夹断直径10厘米的钢管。移动缓慢但防御极高，常堵塞通道形成天然路障。</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
         <is>
           <t>[{"type": "mycelium", "min": 10, "max": 22}]</t>
         </is>
@@ -1058,22 +1022,19 @@
         <v>60</v>
       </c>
       <c r="H11" t="n">
-        <v>8</v>
-      </c>
-      <c r="I11" t="n">
         <v>55</v>
       </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>受到辐射后基因链断裂又重组的变异蜂类，尾针注入的毒素可导致神经系统短暂紊乱。攻击时发出高频嗡鸣，令人头晕目眩。</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
-        <is>
-          <t>受到辐射后基因链断裂又重组的变异蜂类，尾针注入的毒素可导致神经系统短暂紊乱。攻击时发出高频嗡鸣，令人头晕目眩。</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
         <is>
           <t>[{"type": "mycelium", "min": 4, "max": 12}]</t>
         </is>
@@ -1112,22 +1073,19 @@
         <v>35</v>
       </c>
       <c r="H12" t="n">
-        <v>70</v>
-      </c>
-      <c r="I12" t="n">
         <v>8</v>
       </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>背甲与矿岩完全融合的巨型陆龟，移动时地面产生细微震动。缩入壳中时防御力提升200%，是废土上最难击杀的低级变异生物之一。</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
-        <is>
-          <t>背甲与矿岩完全融合的巨型陆龟，移动时地面产生细微震动。缩入壳中时防御力提升200%，是废土上最难击杀的低级变异生物之一。</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
         <is>
           <t>[{"type": "mycelium", "min": 10, "max": 25}]</t>
         </is>
@@ -1166,22 +1124,19 @@
         <v>30</v>
       </c>
       <c r="H13" t="n">
-        <v>10</v>
-      </c>
-      <c r="I13" t="n">
         <v>60</v>
       </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>携带高浓度毒素微粒的变异苍蝇，飞行轨迹留下持续30秒的有毒尾迹。虽攻击力微弱，但其毒素可导致持续性的呼吸系统损伤。</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
-        <is>
-          <t>携带高浓度毒素微粒的变异苍蝇，飞行轨迹留下持续30秒的有毒尾迹。虽攻击力微弱，但其毒素可导致持续性的呼吸系统损伤。</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
         <is>
           <t>[{"type": "mycelium", "min": 2, "max": 8}]</t>
         </is>
@@ -1220,22 +1175,19 @@
         <v>130</v>
       </c>
       <c r="H14" t="n">
-        <v>65</v>
-      </c>
-      <c r="I14" t="n">
         <v>85</v>
       </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>["SK_E_L001", "SK_E_L002"]</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>["SK_E_L001", "SK_E_L002"]</t>
+          <t>曾是矿区精英侦察兵，辐射暴露后意识逐渐消散，仅保留猎杀本能。手持改装过的等离子猎弓，射程可达800米，箭矢附带高温燃烧效果。行动模式仍残留战术素养，会利用地形进行伏击。</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
-        <is>
-          <t>曾是矿区精英侦察兵，辐射暴露后意识逐渐消散，仅保留猎杀本能。手持改装过的等离子猎弓，射程可达800米，箭矢附带高温燃烧效果。行动模式仍残留战术素养，会利用地形进行伏击。</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
         <is>
           <t>[{"type": "mycelium", "min": 20, "max": 40}, {"type": "sourceCore", "min": 1, "max": 3}]</t>
         </is>
@@ -1274,22 +1226,19 @@
         <v>90</v>
       </c>
       <c r="H15" t="n">
-        <v>140</v>
-      </c>
-      <c r="I15" t="n">
         <v>45</v>
       </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>["SK_E_L003", "SK_E_L004"]</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>["SK_E_L003", "SK_E_L004"]</t>
+          <t>沉没水城前守备队队长，身穿重型潜水作战服，意识丧失后仍执行巡逻指令。右臂已与水下切割工具融合，单次挥击可切开15厘米厚的合金钢板。</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
-        <is>
-          <t>沉没水城前守备队队长，身穿重型潜水作战服，意识丧失后仍执行巡逻指令。右臂已与水下切割工具融合，单次挥击可切开15厘米厚的合金钢板。</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
         <is>
           <t>[{"type": "mycelium", "min": 25, "max": 50}, {"type": "sourceCore", "min": 2, "max": 5}]</t>
         </is>
@@ -1328,22 +1277,19 @@
         <v>160</v>
       </c>
       <c r="H16" t="n">
-        <v>50</v>
-      </c>
-      <c r="I16" t="n">
         <v>95</v>
       </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>["SK_E_L005", "SK_E_L006"]</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>["SK_E_L005", "SK_E_L006"]</t>
+          <t>腐化丛林研究站首席生物学家，过度接触变异孢子后精神崩溃。脑部与便携式生物分析仪融合，可释放定向超声波攻击，频率足以震碎普通防护面罩。</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
-        <is>
-          <t>腐化丛林研究站首席生物学家，过度接触变异孢子后精神崩溃。脑部与便携式生物分析仪融合，可释放定向超声波攻击，频率足以震碎普通防护面罩。</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
         <is>
           <t>[{"type": "mycelium", "min": 18, "max": 35}, {"type": "sourceCore", "min": 1, "max": 4}]</t>
         </is>
@@ -1382,22 +1328,19 @@
         <v>120</v>
       </c>
       <c r="H17" t="n">
-        <v>110</v>
-      </c>
-      <c r="I17" t="n">
         <v>60</v>
       </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>["SK_E_L007", "SK_E_L008"]</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>["SK_E_L007", "SK_E_L008"]</t>
+          <t>深海遗迹维护工程师，被暗能侵蚀后与水下维修机甲融为一体。胸口的源核反应堆提供源源不断的能量，双臂可发射高能焊接光束。</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
-        <is>
-          <t>深海遗迹维护工程师，被暗能侵蚀后与水下维修机甲融为一体。胸口的源核反应堆提供源源不断的能量，双臂可发射高能焊接光束。</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
         <is>
           <t>[{"type": "mycelium", "min": 22, "max": 45}, {"type": "sourceCore", "min": 2, "max": 4}]</t>
         </is>
@@ -1436,22 +1379,19 @@
         <v>180</v>
       </c>
       <c r="H18" t="n">
-        <v>130</v>
-      </c>
-      <c r="I18" t="n">
         <v>70</v>
       </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>["SK_E_L009", "SK_E_L010"]</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>["SK_E_L009", "SK_E_L010"]</t>
+          <t>军事要塞前战术指挥官，大脑被军用神经芯片接管后成为最危险的失心者之一。全身植入战斗强化外骨骼，可同时操控3台无人战斗单位。</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
-        <is>
-          <t>军事要塞前战术指挥官，大脑被军用神经芯片接管后成为最危险的失心者之一。全身植入战斗强化外骨骼，可同时操控3台无人战斗单位。</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
         <is>
           <t>[{"type": "mycelium", "min": 30, "max": 60}, {"type": "sourceCore", "min": 3, "max": 6}]</t>
         </is>
@@ -1490,22 +1430,19 @@
         <v>100</v>
       </c>
       <c r="H19" t="n">
-        <v>80</v>
-      </c>
-      <c r="I19" t="n">
         <v>75</v>
       </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>["SK_E_L011", "SK_E_L012"]</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>["SK_E_L011", "SK_E_L012"]</t>
+          <t>荧光温泉医疗站主治医官，过量接触源核辐射后精神异变。手中的纳米修复枪被改造成生物武器，原本治愈的纳米机器人变为侵蚀性纳米虫群。</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
-        <is>
-          <t>荧光温泉医疗站主治医官，过量接触源核辐射后精神异变。手中的纳米修复枪被改造成生物武器，原本治愈的纳米机器人变为侵蚀性纳米虫群。</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
         <is>
           <t>[{"type": "mycelium", "min": 20, "max": 40}, {"type": "sourceCore", "min": 2, "max": 5}]</t>
         </is>
@@ -1544,22 +1481,19 @@
         <v>150</v>
       </c>
       <c r="H20" t="n">
-        <v>100</v>
-      </c>
-      <c r="I20" t="n">
         <v>80</v>
       </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>["SK_E_L013", "SK_E_L014"]</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>["SK_E_L013", "SK_E_L014"]</t>
+          <t>机械军火库高级武器技师，意识被武器系统AI同化后成为人形战斗终端。背部安装了4联装微型导弹发射器，可在3秒内完成装填与发射。</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
-        <is>
-          <t>机械军火库高级武器技师，意识被武器系统AI同化后成为人形战斗终端。背部安装了4联装微型导弹发射器，可在3秒内完成装填与发射。</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
         <is>
           <t>[{"type": "mycelium", "min": 25, "max": 50}, {"type": "sourceCore", "min": 2, "max": 5}]</t>
         </is>
@@ -1598,22 +1532,19 @@
         <v>140</v>
       </c>
       <c r="H21" t="n">
-        <v>120</v>
-      </c>
-      <c r="I21" t="n">
         <v>90</v>
       </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>["SK_E_L015", "SK_E_L016"]</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>["SK_E_L015", "SK_E_L016"]</t>
+          <t>方舟核心区首席领航员，脑机接口被异常信号劫持后丧失自我意识。双眼被全息导航界面取代，可释放干扰波使方舟系统产生错误指令。</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
-        <is>
-          <t>方舟核心区首席领航员，脑机接口被异常信号劫持后丧失自我意识。双眼被全息导航界面取代，可释放干扰波使方舟系统产生错误指令。</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
         <is>
           <t>[{"type": "mycelium", "min": 28, "max": 55}, {"type": "sourceCore", "min": 3, "max": 6}]</t>
         </is>
@@ -1652,22 +1583,19 @@
         <v>170</v>
       </c>
       <c r="H22" t="n">
-        <v>115</v>
-      </c>
-      <c r="I22" t="n">
         <v>85</v>
       </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>["SK_E_L017", "SK_E_L018"]</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>["SK_E_L017", "SK_E_L018"]</t>
+          <t>辐射风暴外围哨兵，长期暴露于极端辐射后身体产生不可逆变异。左半身已结晶化为暗色辐射晶体，可释放致命的辐射脉冲波。</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
-        <is>
-          <t>辐射风暴外围哨兵，长期暴露于极端辐射后身体产生不可逆变异。左半身已结晶化为暗色辐射晶体，可释放致命的辐射脉冲波。</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
         <is>
           <t>[{"type": "mycelium", "min": 30, "max": 60}, {"type": "sourceCore", "min": 3, "max": 7}]</t>
         </is>
@@ -1706,22 +1634,19 @@
         <v>200</v>
       </c>
       <c r="H23" t="n">
-        <v>150</v>
-      </c>
-      <c r="I23" t="n">
         <v>95</v>
       </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>["SK_E_L019", "SK_E_L020"]</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>["SK_E_L019", "SK_E_L020"]</t>
+          <t>终焉之地最早的探索者之一，被未知暗能完全吞噬后成为最强大的失心者。全身被暗物质包裹，可操控空间扭曲产生引力塌缩，是接近Boss级别的存在。</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
-        <is>
-          <t>终焉之地最早的探索者之一，被未知暗能完全吞噬后成为最强大的失心者。全身被暗物质包裹，可操控空间扭曲产生引力塌缩，是接近Boss级别的存在。</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
         <is>
           <t>[{"type": "mycelium", "min": 40, "max": 80}, {"type": "sourceCore", "min": 5, "max": 10}]</t>
         </is>
